--- a/artfynd/A 4180-2022 artfynd.xlsx
+++ b/artfynd/A 4180-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4180-2022 artfynd.xlsx
+++ b/artfynd/A 4180-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7229152</v>
+        <v>7229151</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508296.7303096754</v>
+        <v>508297</v>
       </c>
       <c r="R2" t="n">
-        <v>6954148.823854185</v>
+        <v>6954149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,21 +757,11 @@
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -788,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog på frisk mossig mark</t>
+          <t>Blåbärsgranskog på fuktig mossig mark. Skogsfräken</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,47 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7229153</v>
+        <v>7229154</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>620</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -860,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508195.2493363266</v>
+        <v>508180</v>
       </c>
       <c r="R3" t="n">
-        <v>6954129.302066</v>
+        <v>6954141</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,21 +873,11 @@
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -919,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog på frisk mossig mark</t>
+          <t>Blandskogkärr på fuktig tuvig vitmossemark. Skogsfräken.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,42 +907,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55265231</v>
+        <v>7229155</v>
       </c>
       <c r="B4" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,21 +945,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sidsjöns utlopp, 1,8 km SO, Jmt</t>
+          <t>Sundsveområtet, Sidsjö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508107.3735432333</v>
+        <v>508155</v>
       </c>
       <c r="R4" t="n">
-        <v>6954181.383315634</v>
+        <v>6954103</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,22 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,13 +1005,13 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>luckig granskog med översilad rännilar på vitmossor</t>
+          <t>Granskogkärr på fuktig tuvig vitmossemark. Skogsfräken.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Bo Norell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1065,64 +1023,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55265241</v>
+        <v>95841827</v>
       </c>
       <c r="B5" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>620</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sidsjöns utlopp, 1,85 km SO, Jmt</t>
+          <t>Sundsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508177.3619562636</v>
+        <v>508214</v>
       </c>
       <c r="R5" t="n">
-        <v>6954117.329803777</v>
+        <v>6954151</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,27 +1100,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-07-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>knärot</t>
+          <t>En stjälk vissnad.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,70 +1119,61 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>luckig granskog med översilande vatten</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Norell</t>
+          <t>Lars Grönvik</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7229151</v>
+        <v>7229152</v>
       </c>
       <c r="B6" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>620</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1252,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508296.7303096754</v>
+        <v>508297</v>
       </c>
       <c r="R6" t="n">
-        <v>6954148.823854185</v>
+        <v>6954149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,21 +1220,11 @@
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1311,7 +1236,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog på fuktig mossig mark. Skogsfräken</t>
+          <t>Blåbärsgranskog på frisk mossig mark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,47 +1254,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7229154</v>
+        <v>7229153</v>
       </c>
       <c r="B7" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>620</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1383,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508180.0592338752</v>
+        <v>508195</v>
       </c>
       <c r="R7" t="n">
-        <v>6954141.192147363</v>
+        <v>6954129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1416,21 +1336,11 @@
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-07-31</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1442,7 +1352,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Blandskogkärr på fuktig tuvig vitmossemark. Skogsfräken.</t>
+          <t>Blåbärsgranskog på frisk mossig mark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1460,42 +1370,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95841827</v>
+        <v>7229163</v>
       </c>
       <c r="B8" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>620</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1503,22 +1408,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsmyren, Jmt</t>
+          <t>Sidsjöbergets norrsida, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508214.031399726</v>
+        <v>508025</v>
       </c>
       <c r="R8" t="n">
-        <v>6954150.910576588</v>
+        <v>6954130</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,27 +1449,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En stjälk vissnad.</t>
+          <t>2013-07-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,22 +1463,257 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Granskog på sluttande mossig mark.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Bo Norell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Bo Norell</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>55265231</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sidsjöns utlopp, 1,8 km SO, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>508107</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6954181</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>luckig granskog med översilad rännilar på vitmossor</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>55265241</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sidsjöns utlopp, 1,85 km SO, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>508177</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6954117</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-07-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>knärot</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>luckig granskog med översilande vatten</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4180-2022 artfynd.xlsx
+++ b/artfynd/A 4180-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95841827</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229152</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7229163</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,6 +1636,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55265231</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1714,8 +1759,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55265241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>